--- a/diseases/d116/2026-2029.xlsx
+++ b/diseases/d116/2026-2029.xlsx
@@ -1602,7 +1602,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -5896,7 +5896,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7440,7 +7440,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -7990,7 +7990,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -8540,7 +8540,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -9090,7 +9090,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10084,7 +10084,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -10634,7 +10634,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -11184,7 +11184,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -11734,7 +11734,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -12728,7 +12728,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -13278,7 +13278,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -13828,7 +13828,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -14378,7 +14378,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -14928,7 +14928,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -15376,16 +15376,16 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O85" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q85" t="n">
         <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>0.01303707733931069</v>
+        <v>0.01738276978574758</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -16472,7 +16472,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -17022,7 +17022,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
@@ -17572,7 +17572,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -18418,7 +18418,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -18968,7 +18968,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -19518,7 +19518,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -20068,7 +20068,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -20479,7 +20479,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d116/2026-2029.xlsx
+++ b/diseases/d116/2026-2029.xlsx
@@ -1602,7 +1602,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -5896,7 +5896,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7440,7 +7440,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -7990,7 +7990,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -8540,7 +8540,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -9090,7 +9090,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10084,7 +10084,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -10634,7 +10634,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -11184,7 +11184,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -11734,7 +11734,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -12728,7 +12728,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -13278,7 +13278,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -13828,7 +13828,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -14378,7 +14378,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -14928,7 +14928,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -16472,7 +16472,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -17022,7 +17022,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
@@ -17572,7 +17572,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -18418,7 +18418,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -18968,7 +18968,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -19518,7 +19518,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -20068,7 +20068,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">

--- a/diseases/d116/2026-2029.xlsx
+++ b/diseases/d116/2026-2029.xlsx
@@ -20301,6 +20301,408 @@
         </is>
       </c>
     </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>melioidosis</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>类鼻疽</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N113" t="n">
+        <v>0</v>
+      </c>
+      <c r="O113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P113" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>0</v>
+      </c>
+      <c r="R113" t="n">
+        <v>0</v>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO113" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP113" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ113" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS113" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT113" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU113" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV113" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA113" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB113" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC113" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>melioidosis</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>类鼻疽</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N114" t="n">
+        <v>0</v>
+      </c>
+      <c r="O114" t="n">
+        <v>0</v>
+      </c>
+      <c r="P114" t="n">
+        <v>0</v>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X114" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD114" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE114" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF114" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG114" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH114" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI114" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ114" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK114" t="inlineStr">
+        <is>
+          <t>Japan NIID melioidosis notifications; not glanders.</t>
+        </is>
+      </c>
+      <c r="AM114" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN114" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO114" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP114" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ114" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS114" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT114" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU114" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV114" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA114" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB114" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC114" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -20334,7 +20736,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -20417,7 +20819,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10">
@@ -20427,7 +20829,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11">
@@ -20447,7 +20849,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d116/2026-2029.xlsx
+++ b/diseases/d116/2026-2029.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>2</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0.02710540560393419</v>
       </c>
@@ -913,9 +910,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -1360,9 +1354,6 @@
       <c r="P6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -1612,7 +1603,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2162,7 +2153,7 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN10" t="b">
@@ -2712,7 +2703,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3262,7 +3253,7 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN16" t="b">
@@ -3557,9 +3548,6 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
@@ -3960,7 +3948,7 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN20" t="b">
@@ -4107,9 +4095,6 @@
       <c r="O21" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
@@ -4806,7 +4791,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -5356,7 +5341,7 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN28" t="b">
@@ -5906,7 +5891,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -6201,9 +6186,6 @@
       <c r="O33" t="n">
         <v>3</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0.04065810840590128</v>
       </c>
@@ -6604,7 +6586,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -6751,9 +6733,6 @@
       <c r="O36" t="n">
         <v>1</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0.001937969923792046</v>
       </c>
@@ -7450,7 +7429,7 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN40" t="b">
@@ -8000,7 +7979,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -8550,7 +8529,7 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN46" t="b">
@@ -9100,7 +9079,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -9247,9 +9226,6 @@
       <c r="O50" t="n">
         <v>1</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -9395,9 +9371,6 @@
       <c r="O51" t="n">
         <v>0</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
@@ -9543,9 +9516,6 @@
       <c r="O52" t="n">
         <v>2</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0.008691384892873792</v>
       </c>
@@ -10094,7 +10064,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -10644,7 +10614,7 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN58" t="b">
@@ -11194,7 +11164,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -11744,7 +11714,7 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN64" t="b">
@@ -11891,9 +11861,6 @@
       <c r="O65" t="n">
         <v>0</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
@@ -12039,9 +12006,6 @@
       <c r="O66" t="n">
         <v>0</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0</v>
       </c>
@@ -12187,9 +12151,6 @@
       <c r="O67" t="n">
         <v>2</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0.008691384892873792</v>
       </c>
@@ -12738,7 +12699,7 @@
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN70" t="b">
@@ -13288,7 +13249,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -13838,7 +13799,7 @@
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN76" t="b">
@@ -14388,7 +14349,7 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN79" t="b">
@@ -14938,7 +14899,7 @@
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN82" t="b">
@@ -15085,9 +15046,6 @@
       <c r="O83" t="n">
         <v>1</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -15233,9 +15191,6 @@
       <c r="O84" t="n">
         <v>0</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0</v>
       </c>
@@ -15376,16 +15331,13 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O85" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q85" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R85" t="n">
-        <v>0.01738276978574758</v>
+        <v>0.01303707733931069</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -15529,9 +15481,6 @@
       <c r="O86" t="n">
         <v>0</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0</v>
       </c>
@@ -15680,9 +15629,6 @@
       <c r="P87" t="n">
         <v>0</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0</v>
       </c>
@@ -15932,7 +15878,7 @@
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN88" t="b">
@@ -16079,9 +16025,6 @@
       <c r="O89" t="n">
         <v>0</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0</v>
       </c>
@@ -16230,9 +16173,6 @@
       <c r="P90" t="n">
         <v>0</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0</v>
       </c>
@@ -16482,7 +16422,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -16629,9 +16569,6 @@
       <c r="O92" t="n">
         <v>0</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0</v>
       </c>
@@ -16780,9 +16717,6 @@
       <c r="P93" t="n">
         <v>0</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0</v>
       </c>
@@ -17032,7 +16966,7 @@
       </c>
       <c r="AM94" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN94" t="b">
@@ -17179,9 +17113,6 @@
       <c r="O95" t="n">
         <v>0</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0</v>
       </c>
@@ -17330,9 +17261,6 @@
       <c r="P96" t="n">
         <v>0</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0</v>
       </c>
@@ -17582,7 +17510,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -17729,9 +17657,6 @@
       <c r="O98" t="n">
         <v>0</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0</v>
       </c>
@@ -17877,9 +17802,6 @@
       <c r="O99" t="n">
         <v>5</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0.02172846223218448</v>
       </c>
@@ -18025,9 +17947,6 @@
       <c r="O100" t="n">
         <v>0</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0</v>
       </c>
@@ -18176,9 +18095,6 @@
       <c r="P101" t="n">
         <v>0</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0</v>
       </c>
@@ -18428,7 +18344,7 @@
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN102" t="b">
@@ -18575,9 +18491,6 @@
       <c r="O103" t="n">
         <v>0</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0</v>
       </c>
@@ -18726,9 +18639,6 @@
       <c r="P104" t="n">
         <v>0</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0</v>
       </c>
@@ -18978,7 +18888,7 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN105" t="b">
@@ -19125,9 +19035,6 @@
       <c r="O106" t="n">
         <v>0</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0</v>
       </c>
@@ -19276,9 +19183,6 @@
       <c r="P107" t="n">
         <v>1</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0.0008168084075657662</v>
       </c>
@@ -19528,7 +19432,7 @@
       </c>
       <c r="AM108" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN108" t="b">
@@ -19675,9 +19579,6 @@
       <c r="O109" t="n">
         <v>0</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0</v>
       </c>
@@ -19826,9 +19727,6 @@
       <c r="P110" t="n">
         <v>0</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0</v>
       </c>
@@ -20078,7 +19976,7 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN111" t="b">
@@ -20225,9 +20123,6 @@
       <c r="O112" t="n">
         <v>0</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0</v>
       </c>
@@ -20376,9 +20271,6 @@
       <c r="P113" t="n">
         <v>0</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0</v>
       </c>
@@ -20628,7 +20520,7 @@
       </c>
       <c r="AM114" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN114" t="b">
@@ -20881,7 +20773,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d116/2026-2029.xlsx
+++ b/diseases/d116/2026-2029.xlsx
@@ -20595,6 +20595,405 @@
         </is>
       </c>
     </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>melioidosis</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>类鼻疽</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N115" t="n">
+        <v>0</v>
+      </c>
+      <c r="O115" t="n">
+        <v>0</v>
+      </c>
+      <c r="P115" t="n">
+        <v>0</v>
+      </c>
+      <c r="R115" t="n">
+        <v>0</v>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO115" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP115" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ115" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS115" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT115" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU115" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV115" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA115" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB115" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC115" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>melioidosis</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>类鼻疽</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N116" t="n">
+        <v>0</v>
+      </c>
+      <c r="O116" t="n">
+        <v>0</v>
+      </c>
+      <c r="P116" t="n">
+        <v>0</v>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X116" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD116" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE116" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF116" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG116" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH116" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI116" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ116" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK116" t="inlineStr">
+        <is>
+          <t>Japan NIID melioidosis notifications; not glanders.</t>
+        </is>
+      </c>
+      <c r="AM116" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN116" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO116" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP116" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ116" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS116" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT116" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU116" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV116" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA116" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB116" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC116" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -20628,7 +21027,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -20711,7 +21110,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10">
@@ -20721,7 +21120,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11">
@@ -20741,7 +21140,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d116/2026-2029.xlsx
+++ b/diseases/d116/2026-2029.xlsx
@@ -20994,6 +20994,405 @@
         </is>
       </c>
     </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>melioidosis</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>类鼻疽</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N117" t="n">
+        <v>0</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0</v>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO117" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP117" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ117" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS117" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT117" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU117" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV117" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA117" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB117" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC117" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>melioidosis</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>类鼻疽</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N118" t="n">
+        <v>0</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0</v>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X118" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD118" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE118" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF118" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG118" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI118" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>Japan NIID melioidosis notifications; not glanders.</t>
+        </is>
+      </c>
+      <c r="AM118" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN118" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO118" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP118" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ118" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS118" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT118" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU118" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV118" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA118" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB118" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC118" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -21027,7 +21426,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -21110,7 +21509,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10">
@@ -21120,7 +21519,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11">
@@ -21140,7 +21539,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d116/2026-2029.xlsx
+++ b/diseases/d116/2026-2029.xlsx
@@ -1593,7 +1593,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4425,7 +4425,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7695,7 +7695,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -8639,7 +8639,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9728,7 +9728,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10965,7 +10965,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -11909,7 +11909,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -12853,7 +12853,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
@@ -13797,7 +13797,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15176,7 +15176,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16120,7 +16120,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
@@ -17064,7 +17064,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18008,7 +18008,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -19387,7 +19387,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -20331,7 +20331,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -21275,7 +21275,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -22219,7 +22219,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -23163,7 +23163,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -24536,7 +24536,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -25474,7 +25474,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -26412,7 +26412,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -27350,7 +27350,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -28578,7 +28578,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -29516,7 +29516,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -30454,7 +30454,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK164" t="inlineStr">
@@ -31392,7 +31392,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -32330,7 +32330,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -33123,7 +33123,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK178" t="inlineStr">
@@ -33916,7 +33916,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK182" t="inlineStr">

--- a/diseases/d116/2026-2029.xlsx
+++ b/diseases/d116/2026-2029.xlsx
@@ -1593,7 +1593,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4425,7 +4425,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7695,7 +7695,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -8639,7 +8639,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9728,7 +9728,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10965,7 +10965,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -11909,7 +11909,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -12853,7 +12853,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
@@ -13797,7 +13797,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15176,7 +15176,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16120,7 +16120,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
@@ -17064,7 +17064,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18008,7 +18008,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -19387,7 +19387,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -20331,7 +20331,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -21275,7 +21275,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -22219,7 +22219,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -23163,7 +23163,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -24536,7 +24536,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -25474,7 +25474,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -26412,7 +26412,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -27350,7 +27350,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -28578,7 +28578,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -29516,7 +29516,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -30454,7 +30454,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK164" t="inlineStr">
@@ -31392,7 +31392,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -32330,7 +32330,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -33123,7 +33123,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK178" t="inlineStr">
@@ -33916,7 +33916,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK182" t="inlineStr">

--- a/diseases/d116/2026-2029.xlsx
+++ b/diseases/d116/2026-2029.xlsx
@@ -27857,12 +27857,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -27935,42 +27935,42 @@
       </c>
       <c r="AV150" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA150" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB150" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC150" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -28002,12 +28002,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -28041,13 +28041,13 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O151" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R151" t="n">
-        <v>0.02172846223218448</v>
+        <v>0</v>
       </c>
       <c r="S151" t="inlineStr">
         <is>
@@ -28080,42 +28080,42 @@
       </c>
       <c r="AV151" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA151" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB151" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC151" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -28147,12 +28147,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -28177,7 +28177,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -28186,13 +28186,13 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O152" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R152" t="n">
-        <v>0</v>
+        <v>0.02172846223218448</v>
       </c>
       <c r="S152" t="inlineStr">
         <is>
@@ -28225,42 +28225,42 @@
       </c>
       <c r="AV152" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA152" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB152" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC152" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -28292,12 +28292,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -28322,7 +28322,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -28336,9 +28336,6 @@
       <c r="O153" t="n">
         <v>0</v>
       </c>
-      <c r="P153" t="n">
-        <v>0</v>
-      </c>
       <c r="R153" t="n">
         <v>0</v>
       </c>
@@ -28347,82 +28344,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U153" t="inlineStr">
-        <is>
-          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA153" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO153" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP153" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ153" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS153" t="inlineStr">
-        <is>
-          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR153" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS153" t="inlineStr"/>
       <c r="AT153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU153" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV153" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA153" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB153" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC153" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -28449,7 +28432,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -28501,98 +28484,23 @@
       <c r="P154" t="n">
         <v>0</v>
       </c>
+      <c r="R154" t="n">
+        <v>0</v>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U154" t="inlineStr">
         <is>
           <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V154" t="inlineStr">
-        <is>
-          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W154" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X154" t="inlineStr">
-        <is>
-          <t>Melioidosis</t>
-        </is>
-      </c>
-      <c r="Y154" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z154" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB154" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC154" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD154" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE154" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF154" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG154" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH154" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI154" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ154" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK154" t="inlineStr">
-        <is>
-          <t>Japan NIID melioidosis notifications; not glanders.</t>
-        </is>
-      </c>
-      <c r="AM154" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN154" t="b">
-        <v>1</v>
       </c>
       <c r="AO154" t="inlineStr">
         <is>
@@ -28686,17 +28594,17 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -28730,20 +28638,42 @@
         </is>
       </c>
       <c r="N155" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O155" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P155" t="n">
-        <v>2</v>
-      </c>
-      <c r="R155" t="n">
-        <v>0.03386531510194095</v>
-      </c>
-      <c r="S155" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>0</v>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X155" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -28751,6 +28681,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD155" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE155" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF155" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG155" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH155" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI155" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ155" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK155" t="inlineStr">
+        <is>
+          <t>Japan NIID melioidosis notifications; not glanders.</t>
+        </is>
+      </c>
+      <c r="AM155" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN155" t="b">
+        <v>1</v>
+      </c>
       <c r="AO155" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -28758,7 +28746,7 @@
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ155" t="inlineStr">
@@ -28768,55 +28756,55 @@
       </c>
       <c r="AS155" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_MELIOIDOSIS; SER_SG_HIST_MELIOIDOSIS</t>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT155" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU155" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV155" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA155" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB155" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC155" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -28843,7 +28831,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -28895,98 +28883,18 @@
       <c r="P156" t="n">
         <v>2</v>
       </c>
-      <c r="U156" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MELIOIDOSIS</t>
-        </is>
-      </c>
-      <c r="V156" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MELIOIDOSIS</t>
-        </is>
-      </c>
-      <c r="W156" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X156" t="inlineStr">
-        <is>
-          <t>Melioidosis</t>
-        </is>
-      </c>
-      <c r="Y156" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z156" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R156" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB156" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD156" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE156" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF156" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG156" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH156" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI156" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ156" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK156" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM156" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN156" t="b">
-        <v>1</v>
       </c>
       <c r="AO156" t="inlineStr">
         <is>
@@ -29080,17 +28988,17 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -29115,7 +29023,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
@@ -29124,81 +29032,173 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O157" t="n">
-        <v>0</v>
-      </c>
-      <c r="R157" t="n">
-        <v>0</v>
-      </c>
-      <c r="S157" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="P157" t="n">
+        <v>2</v>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MELIOIDOSIS</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MELIOIDOSIS</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X157" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD157" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE157" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF157" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG157" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI157" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ157" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK157" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM157" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN157" t="b">
+        <v>1</v>
       </c>
       <c r="AO157" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR157" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS157" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ157" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS157" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MELIOIDOSIS; SER_SG_HIST_MELIOIDOSIS</t>
+        </is>
+      </c>
       <c r="AT157" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU157" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV157" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA157" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB157" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC157" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -29230,12 +29230,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -29260,7 +29260,7 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
@@ -29274,9 +29274,6 @@
       <c r="O158" t="n">
         <v>0</v>
       </c>
-      <c r="P158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>0</v>
       </c>
@@ -29285,82 +29282,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U158" t="inlineStr">
-        <is>
-          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA158" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO158" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP158" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ158" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS158" t="inlineStr">
-        <is>
-          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR158" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS158" t="inlineStr"/>
       <c r="AT158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU158" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV158" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA158" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB158" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC158" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -29387,7 +29370,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -29439,98 +29422,23 @@
       <c r="P159" t="n">
         <v>0</v>
       </c>
+      <c r="R159" t="n">
+        <v>0</v>
+      </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U159" t="inlineStr">
         <is>
           <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V159" t="inlineStr">
-        <is>
-          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W159" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X159" t="inlineStr">
-        <is>
-          <t>Melioidosis</t>
-        </is>
-      </c>
-      <c r="Y159" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z159" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB159" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC159" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD159" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE159" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF159" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG159" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH159" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI159" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ159" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK159" t="inlineStr">
-        <is>
-          <t>Japan NIID melioidosis notifications; not glanders.</t>
-        </is>
-      </c>
-      <c r="AM159" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN159" t="b">
-        <v>1</v>
       </c>
       <c r="AO159" t="inlineStr">
         <is>
@@ -29624,17 +29532,17 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -29676,12 +29584,34 @@
       <c r="P160" t="n">
         <v>0</v>
       </c>
-      <c r="R160" t="n">
-        <v>0</v>
-      </c>
-      <c r="S160" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W160" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X160" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -29689,6 +29619,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB160" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD160" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE160" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF160" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG160" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH160" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI160" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ160" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK160" t="inlineStr">
+        <is>
+          <t>Japan NIID melioidosis notifications; not glanders.</t>
+        </is>
+      </c>
+      <c r="AM160" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN160" t="b">
+        <v>1</v>
+      </c>
       <c r="AO160" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -29696,7 +29684,7 @@
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ160" t="inlineStr">
@@ -29706,55 +29694,55 @@
       </c>
       <c r="AS160" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_MELIOIDOSIS; SER_SG_HIST_MELIOIDOSIS</t>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT160" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU160" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV160" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA160" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB160" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC160" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -29781,7 +29769,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -29833,98 +29821,18 @@
       <c r="P161" t="n">
         <v>0</v>
       </c>
-      <c r="U161" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MELIOIDOSIS</t>
-        </is>
-      </c>
-      <c r="V161" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MELIOIDOSIS</t>
-        </is>
-      </c>
-      <c r="W161" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X161" t="inlineStr">
-        <is>
-          <t>Melioidosis</t>
-        </is>
-      </c>
-      <c r="Y161" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z161" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R161" t="n">
+        <v>0</v>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB161" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC161" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD161" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE161" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF161" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG161" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH161" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI161" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ161" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK161" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM161" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN161" t="b">
-        <v>1</v>
       </c>
       <c r="AO161" t="inlineStr">
         <is>
@@ -30018,17 +29926,17 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -30053,7 +29961,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
@@ -30067,76 +29975,168 @@
       <c r="O162" t="n">
         <v>0</v>
       </c>
-      <c r="R162" t="n">
-        <v>0</v>
-      </c>
-      <c r="S162" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P162" t="n">
+        <v>0</v>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MELIOIDOSIS</t>
+        </is>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MELIOIDOSIS</t>
+        </is>
+      </c>
+      <c r="W162" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X162" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD162" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE162" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF162" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG162" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH162" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI162" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ162" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK162" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM162" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN162" t="b">
+        <v>1</v>
       </c>
       <c r="AO162" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR162" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS162" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ162" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS162" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MELIOIDOSIS; SER_SG_HIST_MELIOIDOSIS</t>
+        </is>
+      </c>
       <c r="AT162" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU162" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV162" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA162" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB162" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC162" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -30168,12 +30168,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -30198,7 +30198,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -30207,98 +30207,81 @@
         </is>
       </c>
       <c r="N163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O163" t="n">
-        <v>1</v>
-      </c>
-      <c r="P163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R163" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0</v>
       </c>
       <c r="S163" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U163" t="inlineStr">
-        <is>
-          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA163" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO163" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP163" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ163" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS163" t="inlineStr">
-        <is>
-          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR163" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS163" t="inlineStr"/>
       <c r="AT163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU163" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV163" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA163" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB163" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC163" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -30325,7 +30308,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -30377,98 +30360,23 @@
       <c r="P164" t="n">
         <v>1</v>
       </c>
+      <c r="R164" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U164" t="inlineStr">
         <is>
           <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V164" t="inlineStr">
-        <is>
-          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W164" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X164" t="inlineStr">
-        <is>
-          <t>Melioidosis</t>
-        </is>
-      </c>
-      <c r="Y164" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z164" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA164" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB164" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC164" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD164" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE164" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF164" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG164" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH164" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI164" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ164" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK164" t="inlineStr">
-        <is>
-          <t>Japan NIID melioidosis notifications; not glanders.</t>
-        </is>
-      </c>
-      <c r="AM164" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN164" t="b">
-        <v>1</v>
       </c>
       <c r="AO164" t="inlineStr">
         <is>
@@ -30562,17 +30470,17 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -30606,20 +30514,42 @@
         </is>
       </c>
       <c r="N165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P165" t="n">
-        <v>0</v>
-      </c>
-      <c r="R165" t="n">
-        <v>0</v>
-      </c>
-      <c r="S165" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>1</v>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W165" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X165" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -30627,6 +30557,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB165" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC165" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD165" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE165" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF165" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG165" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH165" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI165" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ165" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK165" t="inlineStr">
+        <is>
+          <t>Japan NIID melioidosis notifications; not glanders.</t>
+        </is>
+      </c>
+      <c r="AM165" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN165" t="b">
+        <v>1</v>
+      </c>
       <c r="AO165" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -30634,7 +30622,7 @@
       </c>
       <c r="AP165" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ165" t="inlineStr">
@@ -30644,55 +30632,55 @@
       </c>
       <c r="AS165" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_MELIOIDOSIS; SER_SG_HIST_MELIOIDOSIS</t>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT165" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU165" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV165" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA165" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB165" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC165" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -30719,7 +30707,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -30771,98 +30759,18 @@
       <c r="P166" t="n">
         <v>0</v>
       </c>
-      <c r="U166" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MELIOIDOSIS</t>
-        </is>
-      </c>
-      <c r="V166" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MELIOIDOSIS</t>
-        </is>
-      </c>
-      <c r="W166" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X166" t="inlineStr">
-        <is>
-          <t>Melioidosis</t>
-        </is>
-      </c>
-      <c r="Y166" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z166" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R166" t="n">
+        <v>0</v>
+      </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB166" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC166" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD166" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE166" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF166" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG166" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH166" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI166" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ166" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK166" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM166" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN166" t="b">
-        <v>1</v>
       </c>
       <c r="AO166" t="inlineStr">
         <is>
@@ -30956,17 +30864,17 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -30991,7 +30899,7 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
@@ -31005,76 +30913,168 @@
       <c r="O167" t="n">
         <v>0</v>
       </c>
-      <c r="R167" t="n">
-        <v>0</v>
-      </c>
-      <c r="S167" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P167" t="n">
+        <v>0</v>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MELIOIDOSIS</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MELIOIDOSIS</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X167" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB167" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD167" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE167" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF167" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG167" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH167" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI167" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ167" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK167" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM167" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN167" t="b">
+        <v>1</v>
       </c>
       <c r="AO167" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR167" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS167" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ167" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS167" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MELIOIDOSIS; SER_SG_HIST_MELIOIDOSIS</t>
+        </is>
+      </c>
       <c r="AT167" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU167" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV167" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA167" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB167" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC167" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -31106,12 +31106,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -31136,7 +31136,7 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
@@ -31150,9 +31150,6 @@
       <c r="O168" t="n">
         <v>0</v>
       </c>
-      <c r="P168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>0</v>
       </c>
@@ -31161,82 +31158,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U168" t="inlineStr">
-        <is>
-          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA168" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO168" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP168" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ168" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS168" t="inlineStr">
-        <is>
-          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR168" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS168" t="inlineStr"/>
       <c r="AT168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU168" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV168" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA168" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB168" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC168" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -31263,7 +31246,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -31315,98 +31298,23 @@
       <c r="P169" t="n">
         <v>0</v>
       </c>
+      <c r="R169" t="n">
+        <v>0</v>
+      </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U169" t="inlineStr">
         <is>
           <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V169" t="inlineStr">
-        <is>
-          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W169" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X169" t="inlineStr">
-        <is>
-          <t>Melioidosis</t>
-        </is>
-      </c>
-      <c r="Y169" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z169" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA169" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB169" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC169" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD169" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE169" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF169" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG169" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH169" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI169" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ169" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK169" t="inlineStr">
-        <is>
-          <t>Japan NIID melioidosis notifications; not glanders.</t>
-        </is>
-      </c>
-      <c r="AM169" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN169" t="b">
-        <v>1</v>
       </c>
       <c r="AO169" t="inlineStr">
         <is>
@@ -31500,17 +31408,17 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -31552,12 +31460,34 @@
       <c r="P170" t="n">
         <v>0</v>
       </c>
-      <c r="R170" t="n">
-        <v>0</v>
-      </c>
-      <c r="S170" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V170" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W170" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X170" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="Y170" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -31565,6 +31495,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB170" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD170" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE170" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF170" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG170" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH170" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI170" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ170" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK170" t="inlineStr">
+        <is>
+          <t>Japan NIID melioidosis notifications; not glanders.</t>
+        </is>
+      </c>
+      <c r="AM170" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN170" t="b">
+        <v>1</v>
+      </c>
       <c r="AO170" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -31572,7 +31560,7 @@
       </c>
       <c r="AP170" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ170" t="inlineStr">
@@ -31582,55 +31570,55 @@
       </c>
       <c r="AS170" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_MELIOIDOSIS; SER_SG_HIST_MELIOIDOSIS</t>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT170" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU170" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV170" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA170" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB170" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC170" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -31657,7 +31645,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -31709,98 +31697,18 @@
       <c r="P171" t="n">
         <v>0</v>
       </c>
-      <c r="U171" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MELIOIDOSIS</t>
-        </is>
-      </c>
-      <c r="V171" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MELIOIDOSIS</t>
-        </is>
-      </c>
-      <c r="W171" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X171" t="inlineStr">
-        <is>
-          <t>Melioidosis</t>
-        </is>
-      </c>
-      <c r="Y171" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z171" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R171" t="n">
+        <v>0</v>
+      </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB171" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC171" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD171" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE171" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF171" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG171" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH171" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI171" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ171" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK171" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM171" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN171" t="b">
-        <v>1</v>
       </c>
       <c r="AO171" t="inlineStr">
         <is>
@@ -31894,17 +31802,17 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -31929,12 +31837,12 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N172" t="n">
@@ -31943,76 +31851,168 @@
       <c r="O172" t="n">
         <v>0</v>
       </c>
-      <c r="R172" t="n">
-        <v>0</v>
-      </c>
-      <c r="S172" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P172" t="n">
+        <v>0</v>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MELIOIDOSIS</t>
+        </is>
+      </c>
+      <c r="V172" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MELIOIDOSIS</t>
+        </is>
+      </c>
+      <c r="W172" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X172" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="Y172" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z172" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB172" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC172" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD172" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE172" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF172" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG172" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH172" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI172" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ172" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK172" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM172" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN172" t="b">
+        <v>1</v>
       </c>
       <c r="AO172" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP172" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR172" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS172" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ172" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS172" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MELIOIDOSIS; SER_SG_HIST_MELIOIDOSIS</t>
+        </is>
+      </c>
       <c r="AT172" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU172" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV172" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA172" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB172" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC172" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -32044,12 +32044,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -32074,7 +32074,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -32088,9 +32088,6 @@
       <c r="O173" t="n">
         <v>0</v>
       </c>
-      <c r="P173" t="n">
-        <v>0</v>
-      </c>
       <c r="R173" t="n">
         <v>0</v>
       </c>
@@ -32099,82 +32096,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U173" t="inlineStr">
-        <is>
-          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA173" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO173" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ173" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS173" t="inlineStr">
-        <is>
-          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR173" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS173" t="inlineStr"/>
       <c r="AT173" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU173" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV173" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA173" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB173" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC173" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -32201,7 +32184,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -32253,98 +32236,23 @@
       <c r="P174" t="n">
         <v>0</v>
       </c>
+      <c r="R174" t="n">
+        <v>0</v>
+      </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U174" t="inlineStr">
         <is>
           <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V174" t="inlineStr">
-        <is>
-          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W174" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X174" t="inlineStr">
-        <is>
-          <t>Melioidosis</t>
-        </is>
-      </c>
-      <c r="Y174" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z174" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA174" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB174" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC174" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD174" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE174" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF174" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG174" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH174" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI174" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ174" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK174" t="inlineStr">
-        <is>
-          <t>Japan NIID melioidosis notifications; not glanders.</t>
-        </is>
-      </c>
-      <c r="AM174" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN174" t="b">
-        <v>1</v>
       </c>
       <c r="AO174" t="inlineStr">
         <is>
@@ -32438,17 +32346,17 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -32482,20 +32390,42 @@
         </is>
       </c>
       <c r="N175" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O175" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P175" t="n">
-        <v>2</v>
-      </c>
-      <c r="R175" t="n">
-        <v>0.03386531510194095</v>
-      </c>
-      <c r="S175" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>0</v>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V175" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W175" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X175" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="Y175" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z175" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -32503,6 +32433,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB175" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC175" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD175" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE175" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF175" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG175" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH175" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI175" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ175" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK175" t="inlineStr">
+        <is>
+          <t>Japan NIID melioidosis notifications; not glanders.</t>
+        </is>
+      </c>
+      <c r="AM175" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN175" t="b">
+        <v>1</v>
+      </c>
       <c r="AO175" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -32510,7 +32498,7 @@
       </c>
       <c r="AP175" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ175" t="inlineStr">
@@ -32520,55 +32508,55 @@
       </c>
       <c r="AS175" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_MELIOIDOSIS; SER_SG_HIST_MELIOIDOSIS</t>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT175" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU175" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV175" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA175" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB175" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC175" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -32595,7 +32583,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -32647,98 +32635,18 @@
       <c r="P176" t="n">
         <v>2</v>
       </c>
-      <c r="U176" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MELIOIDOSIS</t>
-        </is>
-      </c>
-      <c r="V176" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MELIOIDOSIS</t>
-        </is>
-      </c>
-      <c r="W176" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X176" t="inlineStr">
-        <is>
-          <t>Melioidosis</t>
-        </is>
-      </c>
-      <c r="Y176" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z176" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R176" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S176" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB176" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC176" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD176" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE176" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF176" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG176" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH176" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI176" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ176" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK176" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM176" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN176" t="b">
-        <v>1</v>
       </c>
       <c r="AO176" t="inlineStr">
         <is>
@@ -32832,17 +32740,17 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -32867,7 +32775,7 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
@@ -32876,25 +32784,42 @@
         </is>
       </c>
       <c r="N177" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O177" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P177" t="n">
-        <v>0</v>
-      </c>
-      <c r="R177" t="n">
-        <v>0</v>
-      </c>
-      <c r="S177" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
       </c>
       <c r="U177" t="inlineStr">
         <is>
-          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+          <t>SER_SG_CDA_MELIOIDOSIS</t>
+        </is>
+      </c>
+      <c r="V177" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MELIOIDOSIS</t>
+        </is>
+      </c>
+      <c r="W177" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X177" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="Y177" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z177" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -32902,6 +32827,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB177" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC177" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD177" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE177" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF177" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG177" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH177" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI177" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ177" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK177" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM177" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN177" t="b">
+        <v>1</v>
+      </c>
       <c r="AO177" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -32909,7 +32892,7 @@
       </c>
       <c r="AP177" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ177" t="inlineStr">
@@ -32919,55 +32902,55 @@
       </c>
       <c r="AS177" t="inlineStr">
         <is>
-          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+          <t>SER_SG_CDA_MELIOIDOSIS; SER_SG_HIST_MELIOIDOSIS</t>
         </is>
       </c>
       <c r="AT177" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU177" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV177" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA177" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB177" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC177" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -32994,7 +32977,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -33046,98 +33029,23 @@
       <c r="P178" t="n">
         <v>0</v>
       </c>
+      <c r="R178" t="n">
+        <v>0</v>
+      </c>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U178" t="inlineStr">
         <is>
           <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V178" t="inlineStr">
-        <is>
-          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W178" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X178" t="inlineStr">
-        <is>
-          <t>Melioidosis</t>
-        </is>
-      </c>
-      <c r="Y178" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z178" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA178" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB178" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC178" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD178" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE178" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF178" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG178" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH178" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI178" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ178" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK178" t="inlineStr">
-        <is>
-          <t>Japan NIID melioidosis notifications; not glanders.</t>
-        </is>
-      </c>
-      <c r="AM178" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN178" t="b">
-        <v>1</v>
       </c>
       <c r="AO178" t="inlineStr">
         <is>
@@ -33231,17 +33139,17 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -33275,93 +33183,173 @@
         </is>
       </c>
       <c r="N179" t="n">
+        <v>0</v>
+      </c>
+      <c r="O179" t="n">
+        <v>0</v>
+      </c>
+      <c r="P179" t="n">
+        <v>0</v>
+      </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V179" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W179" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X179" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="Y179" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z179" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB179" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC179" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD179" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE179" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF179" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG179" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH179" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI179" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ179" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK179" t="inlineStr">
+        <is>
+          <t>Japan NIID melioidosis notifications; not glanders.</t>
+        </is>
+      </c>
+      <c r="AM179" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN179" t="b">
         <v>1</v>
       </c>
-      <c r="O179" t="n">
+      <c r="AO179" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP179" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ179" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS179" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT179" t="n">
         <v>1</v>
       </c>
-      <c r="P179" t="n">
-        <v>1</v>
-      </c>
-      <c r="R179" t="n">
-        <v>0.01693265755097047</v>
-      </c>
-      <c r="S179" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA179" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO179" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP179" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ179" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS179" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MELIOIDOSIS; SER_SG_HIST_MELIOIDOSIS</t>
-        </is>
-      </c>
-      <c r="AT179" t="n">
-        <v>2</v>
-      </c>
       <c r="AU179" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV179" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA179" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB179" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC179" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -33388,7 +33376,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -33440,98 +33428,18 @@
       <c r="P180" t="n">
         <v>1</v>
       </c>
-      <c r="U180" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MELIOIDOSIS</t>
-        </is>
-      </c>
-      <c r="V180" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MELIOIDOSIS</t>
-        </is>
-      </c>
-      <c r="W180" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X180" t="inlineStr">
-        <is>
-          <t>Melioidosis</t>
-        </is>
-      </c>
-      <c r="Y180" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z180" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R180" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S180" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB180" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC180" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD180" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE180" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF180" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG180" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH180" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI180" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ180" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK180" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM180" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN180" t="b">
-        <v>1</v>
       </c>
       <c r="AO180" t="inlineStr">
         <is>
@@ -33625,17 +33533,17 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -33660,7 +33568,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -33669,25 +33577,42 @@
         </is>
       </c>
       <c r="N181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P181" t="n">
-        <v>0</v>
-      </c>
-      <c r="R181" t="n">
-        <v>0</v>
-      </c>
-      <c r="S181" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="U181" t="inlineStr">
         <is>
-          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+          <t>SER_SG_CDA_MELIOIDOSIS</t>
+        </is>
+      </c>
+      <c r="V181" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MELIOIDOSIS</t>
+        </is>
+      </c>
+      <c r="W181" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X181" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="Y181" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z181" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
@@ -33695,6 +33620,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB181" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC181" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD181" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE181" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF181" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG181" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH181" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI181" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ181" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK181" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM181" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN181" t="b">
+        <v>1</v>
+      </c>
       <c r="AO181" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -33702,7 +33685,7 @@
       </c>
       <c r="AP181" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ181" t="inlineStr">
@@ -33712,55 +33695,55 @@
       </c>
       <c r="AS181" t="inlineStr">
         <is>
-          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+          <t>SER_SG_CDA_MELIOIDOSIS; SER_SG_HIST_MELIOIDOSIS</t>
         </is>
       </c>
       <c r="AT181" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU181" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV181" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ181" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA181" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB181" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC181" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -33787,7 +33770,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -33839,98 +33822,23 @@
       <c r="P182" t="n">
         <v>0</v>
       </c>
+      <c r="R182" t="n">
+        <v>0</v>
+      </c>
+      <c r="S182" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U182" t="inlineStr">
         <is>
           <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V182" t="inlineStr">
-        <is>
-          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W182" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X182" t="inlineStr">
-        <is>
-          <t>Melioidosis</t>
-        </is>
-      </c>
-      <c r="Y182" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z182" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA182" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB182" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC182" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD182" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE182" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF182" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG182" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH182" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI182" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ182" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK182" t="inlineStr">
-        <is>
-          <t>Japan NIID melioidosis notifications; not glanders.</t>
-        </is>
-      </c>
-      <c r="AM182" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN182" t="b">
-        <v>1</v>
       </c>
       <c r="AO182" t="inlineStr">
         <is>
@@ -34024,17 +33932,17 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -34068,93 +33976,173 @@
         </is>
       </c>
       <c r="N183" t="n">
+        <v>0</v>
+      </c>
+      <c r="O183" t="n">
+        <v>0</v>
+      </c>
+      <c r="P183" t="n">
+        <v>0</v>
+      </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V183" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W183" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X183" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="Y183" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z183" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB183" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC183" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD183" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE183" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF183" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG183" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH183" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI183" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ183" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK183" t="inlineStr">
+        <is>
+          <t>Japan NIID melioidosis notifications; not glanders.</t>
+        </is>
+      </c>
+      <c r="AM183" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN183" t="b">
         <v>1</v>
       </c>
-      <c r="O183" t="n">
+      <c r="AO183" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP183" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ183" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS183" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT183" t="n">
         <v>1</v>
       </c>
-      <c r="P183" t="n">
-        <v>1</v>
-      </c>
-      <c r="R183" t="n">
-        <v>0.01693265755097047</v>
-      </c>
-      <c r="S183" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA183" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO183" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP183" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ183" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS183" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MELIOIDOSIS; SER_SG_HIST_MELIOIDOSIS</t>
-        </is>
-      </c>
-      <c r="AT183" t="n">
-        <v>2</v>
-      </c>
       <c r="AU183" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV183" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ183" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA183" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB183" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC183" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -34181,7 +34169,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -34233,98 +34221,18 @@
       <c r="P184" t="n">
         <v>1</v>
       </c>
-      <c r="U184" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MELIOIDOSIS</t>
-        </is>
-      </c>
-      <c r="V184" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MELIOIDOSIS</t>
-        </is>
-      </c>
-      <c r="W184" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X184" t="inlineStr">
-        <is>
-          <t>Melioidosis</t>
-        </is>
-      </c>
-      <c r="Y184" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z184" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R184" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S184" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB184" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC184" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD184" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE184" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF184" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG184" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH184" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI184" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ184" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK184" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM184" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN184" t="b">
-        <v>1</v>
       </c>
       <c r="AO184" t="inlineStr">
         <is>
@@ -34390,6 +34298,243 @@
         </is>
       </c>
       <c r="BC184" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>melioidosis</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>类鼻疽</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N185" t="n">
+        <v>1</v>
+      </c>
+      <c r="O185" t="n">
+        <v>1</v>
+      </c>
+      <c r="P185" t="n">
+        <v>1</v>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MELIOIDOSIS</t>
+        </is>
+      </c>
+      <c r="V185" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MELIOIDOSIS</t>
+        </is>
+      </c>
+      <c r="W185" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X185" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="Y185" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z185" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB185" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC185" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD185" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE185" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF185" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG185" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH185" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI185" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ185" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK185" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM185" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN185" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO185" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP185" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ185" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS185" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MELIOIDOSIS; SER_SG_HIST_MELIOIDOSIS</t>
+        </is>
+      </c>
+      <c r="AT185" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU185" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV185" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW185" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX185" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY185" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA185" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB185" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC185" t="inlineStr">
         <is>
           <t>official_csv_and_workbook</t>
         </is>
@@ -34511,7 +34656,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10">
@@ -34521,7 +34666,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d116/2026-2029.xlsx
+++ b/diseases/d116/2026-2029.xlsx
@@ -1593,7 +1593,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4425,7 +4425,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7695,7 +7695,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -8639,7 +8639,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9728,7 +9728,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10965,7 +10965,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -11909,7 +11909,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -12853,7 +12853,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
@@ -13797,7 +13797,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15176,7 +15176,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16120,7 +16120,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
@@ -17064,7 +17064,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18008,7 +18008,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -19387,7 +19387,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -20331,7 +20331,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -21275,7 +21275,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -22219,7 +22219,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -23163,7 +23163,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -24536,7 +24536,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -25474,7 +25474,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -26412,7 +26412,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -27350,7 +27350,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -28723,7 +28723,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -29661,7 +29661,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK160" t="inlineStr">
@@ -30599,7 +30599,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -31537,7 +31537,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK170" t="inlineStr">
@@ -32475,7 +32475,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -33268,7 +33268,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -34061,7 +34061,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">

--- a/diseases/d116/2026-2029.xlsx
+++ b/diseases/d116/2026-2029.xlsx
@@ -34540,6 +34540,944 @@
         </is>
       </c>
     </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>melioidosis</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>类鼻疽</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N186" t="n">
+        <v>0</v>
+      </c>
+      <c r="O186" t="n">
+        <v>0</v>
+      </c>
+      <c r="P186" t="n">
+        <v>0</v>
+      </c>
+      <c r="R186" t="n">
+        <v>0</v>
+      </c>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO186" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP186" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ186" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS186" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT186" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU186" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV186" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW186" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX186" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY186" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA186" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB186" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC186" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>melioidosis</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>类鼻疽</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N187" t="n">
+        <v>0</v>
+      </c>
+      <c r="O187" t="n">
+        <v>0</v>
+      </c>
+      <c r="P187" t="n">
+        <v>0</v>
+      </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V187" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W187" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X187" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="Y187" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z187" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB187" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC187" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD187" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE187" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF187" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG187" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH187" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI187" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ187" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK187" t="inlineStr">
+        <is>
+          <t>Japan NIID melioidosis notifications; not glanders.</t>
+        </is>
+      </c>
+      <c r="AM187" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN187" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO187" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP187" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ187" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS187" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT187" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU187" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV187" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW187" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX187" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY187" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA187" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB187" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC187" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>melioidosis</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>类鼻疽</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N188" t="n">
+        <v>0</v>
+      </c>
+      <c r="O188" t="n">
+        <v>0</v>
+      </c>
+      <c r="P188" t="n">
+        <v>0</v>
+      </c>
+      <c r="R188" t="n">
+        <v>0</v>
+      </c>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO188" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP188" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ188" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS188" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MELIOIDOSIS; SER_SG_HIST_MELIOIDOSIS</t>
+        </is>
+      </c>
+      <c r="AT188" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU188" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV188" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW188" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX188" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY188" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA188" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB188" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC188" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>melioidosis</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>类鼻疽</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N189" t="n">
+        <v>0</v>
+      </c>
+      <c r="O189" t="n">
+        <v>0</v>
+      </c>
+      <c r="P189" t="n">
+        <v>0</v>
+      </c>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MELIOIDOSIS</t>
+        </is>
+      </c>
+      <c r="V189" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MELIOIDOSIS</t>
+        </is>
+      </c>
+      <c r="W189" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X189" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="Y189" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z189" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB189" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC189" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD189" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE189" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF189" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG189" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH189" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI189" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ189" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK189" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM189" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN189" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO189" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP189" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ189" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS189" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MELIOIDOSIS; SER_SG_HIST_MELIOIDOSIS</t>
+        </is>
+      </c>
+      <c r="AT189" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU189" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV189" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW189" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX189" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY189" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA189" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB189" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC189" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>melioidosis</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>类鼻疽</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N190" t="n">
+        <v>0</v>
+      </c>
+      <c r="O190" t="n">
+        <v>0</v>
+      </c>
+      <c r="R190" t="n">
+        <v>0</v>
+      </c>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO190" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP190" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR190" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS190" t="inlineStr"/>
+      <c r="AT190" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU190" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV190" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW190" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX190" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY190" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA190" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB190" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC190" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -34573,7 +35511,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -34656,7 +35594,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10">
@@ -34666,7 +35604,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>184</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11">
@@ -34686,7 +35624,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13">
